--- a/annotation/a556.xlsx
+++ b/annotation/a556.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,36 @@
           <t>id</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>kalima_text</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>num_sora</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sora_name_ar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>aya_no</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>kalima_text_emlaey</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -469,6 +499,30 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>يُسَبِّحُ</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>64</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>يسبح</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -489,6 +543,30 @@
       <c r="F3" t="n">
         <v>2</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>لِلَّهِ</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>64</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>لله</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -509,6 +587,30 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>مَا</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>64</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ما</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -529,6 +631,30 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>فِي</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>64</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>في</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,6 +675,30 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ٱلسَّمَٰوَٰتِ</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>64</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>السموات</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +719,30 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وَمَا</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>64</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>وما</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -589,6 +763,30 @@
       <c r="F8" t="n">
         <v>7</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>فِي</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>في</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -609,6 +807,30 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ٱلۡأَرۡضِۖ</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>64</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>الأرض</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,6 +851,30 @@
       <c r="F10" t="n">
         <v>9</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>لَهُ</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>64</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>له</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -649,6 +895,30 @@
       <c r="F11" t="n">
         <v>10</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ٱلۡمُلۡكُ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>64</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>الملك</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -669,6 +939,30 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وَلَهُ</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>64</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>وله</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -689,6 +983,30 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ٱلۡحَمۡدُۖ</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>64</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>الحمد</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,6 +1027,30 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وَهُوَ</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>64</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>وهو</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -729,6 +1071,30 @@
       <c r="F15" t="n">
         <v>14</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>عَلَىٰ</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>64</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>على</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -749,6 +1115,30 @@
       <c r="F16" t="n">
         <v>15</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>كُلِّ</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>64</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>كل</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -769,6 +1159,30 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>شَيۡءٖ</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>64</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>شيء</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -789,6 +1203,30 @@
       <c r="F18" t="n">
         <v>17</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>قَدِيرٌ</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>64</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>قدير</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -807,7 +1245,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>هُوَ</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>64</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>هو</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -827,7 +1289,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ٱلَّذِي</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>64</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>الذي</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -847,7 +1333,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>خَلَقَكُمۡ</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>64</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>خلقكم</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -867,7 +1377,31 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>فَمِنكُمۡ</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>64</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>فمنكم</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -887,7 +1421,31 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>كَافِرٞ</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>64</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>كافر</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -907,7 +1465,31 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وَمِنكُم</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>64</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ومنكم</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -927,7 +1509,31 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>مُّؤۡمِنٞۚ</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>64</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>مؤمن</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -947,7 +1553,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وَٱللَّهُ</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>64</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>والله</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +1597,31 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>بِمَا</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>64</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>بما</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -987,7 +1641,31 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>تَعۡمَلُونَ</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>64</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>تعملون</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1007,7 +1685,31 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>بَصِيرٌ</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>64</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>بصير</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1027,7 +1729,31 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>خَلَقَ</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>64</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>خلق</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1047,7 +1773,31 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ٱلسَّمَٰوَٰتِ</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>64</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>السموات</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1067,7 +1817,31 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وَٱلۡأَرۡضَ</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>64</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>والأرض</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1087,7 +1861,31 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>بِٱلۡحَقِّ</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>64</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>بالحق</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1107,7 +1905,31 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وَصَوَّرَكُمۡ</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>64</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>وصوركم</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1127,7 +1949,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>فَأَحۡسَنَ</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>64</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>فأحسن</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1993,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>صُوَرَكُمۡۖ</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>64</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>صوركم</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1167,7 +2037,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وَإِلَيۡهِ</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>64</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>وإليه</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1187,7 +2081,31 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ٱلۡمَصِيرُ</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>64</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>المصير</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1207,7 +2125,31 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>يَعۡلَمُ</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>64</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>يعلم</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1227,7 +2169,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>مَا</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>64</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ما</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1247,7 +2213,31 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>فِي</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>64</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>في</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1267,7 +2257,31 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ٱلسَّمَٰوَٰتِ</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>64</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>السموات</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1287,7 +2301,31 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وَٱلۡأَرۡضِ</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>64</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>والأرض</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1307,7 +2345,31 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وَيَعۡلَمُ</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>64</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ويعلم</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1327,7 +2389,31 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>مَا</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>64</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ما</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1347,7 +2433,31 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>تُسِرُّونَ</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>64</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>تسرون</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1367,7 +2477,31 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وَمَا</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>64</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>وما</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1387,7 +2521,31 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>تُعۡلِنُونَۚ</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>64</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>تعلنون</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1407,7 +2565,31 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وَٱللَّهُ</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>64</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>والله</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1427,7 +2609,31 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>عَلِيمُۢ</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>64</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>عليم</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1447,7 +2653,31 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>بِذَاتِ</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>64</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>بذات</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1467,7 +2697,31 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ٱلصُّدُورِ</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>64</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>الصدور</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1487,7 +2741,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>أَلَمۡ</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>64</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ألم</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1507,7 +2785,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>يَأۡتِكُمۡ</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>64</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>يأتكم</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1527,7 +2829,31 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>نَبَؤُاْ</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>64</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>نبأ</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1547,7 +2873,31 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ٱلَّذِينَ</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>64</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>الذين</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1567,7 +2917,31 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>كَفَرُواْ</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>64</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>كفروا</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1587,7 +2961,31 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>مِن</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>64</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1607,7 +3005,31 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>قَبۡلُ</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>64</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>قبل</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1627,7 +3049,31 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>فَذَاقُواْ</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>64</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>فذاقوا</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1647,7 +3093,31 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وَبَالَ</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>64</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>وبال</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1667,7 +3137,31 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>أَمۡرِهِمۡ</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>64</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>أمرهم</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1687,7 +3181,31 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وَلَهُمۡ</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>64</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ولهم</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1707,7 +3225,31 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>عَذَابٌ</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>64</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>عذاب</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1727,7 +3269,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>أَلِيمٞ</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>أليم</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1747,7 +3313,31 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>64</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ذلك</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1767,7 +3357,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>بِأَنَّهُۥ</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>64</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>6</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>بأنه</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1787,7 +3401,31 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>كَانَت</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>64</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>كانت</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1807,7 +3445,31 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>تَّأۡتِيهِمۡ</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>64</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>تأتيهم</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1827,7 +3489,31 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>73</v>
+        <v>69</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>رُسُلُهُم</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>64</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>رسلهم</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1847,7 +3533,31 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>بِٱلۡبَيِّنَٰتِ</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>64</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>6</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>بالبينات</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1867,7 +3577,31 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>فَقَالُوٓاْ</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>64</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>فقالوا</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1887,7 +3621,31 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>أَبَشَرٞ</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>64</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>6</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>أبشر</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1907,7 +3665,31 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>يَهۡدُونَنَا</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>64</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>يهدوننا</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1927,7 +3709,31 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>فَكَفَرُواْ</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>64</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>فكفروا</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1947,7 +3753,31 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وَتَوَلَّواْۖ</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>64</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>وتولوا</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1967,7 +3797,31 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وَّٱسۡتَغۡنَى</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>64</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>واستغنى</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1987,7 +3841,31 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ٱللَّهُۚ</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>64</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>6</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2007,7 +3885,31 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وَٱللَّهُ</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>64</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>والله</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2027,7 +3929,31 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>غَنِيٌّ</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>64</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>غني</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2047,7 +3973,31 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>84</v>
+        <v>80</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>حَمِيدٞ</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>64</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>حميد</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2067,7 +4017,31 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>86</v>
+        <v>81</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>زَعَمَ</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>64</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>زعم</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2087,7 +4061,31 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>87</v>
+        <v>82</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ٱلَّذِينَ</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>64</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>الذين</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2107,7 +4105,31 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>كَفَرُوٓاْ</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>64</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>كفروا</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2127,7 +4149,31 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>أَن</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>64</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>أن</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2147,7 +4193,31 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>90</v>
+        <v>85</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>لَّن</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>64</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>لن</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2167,7 +4237,31 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>91</v>
+        <v>86</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>يُبۡعَثُواْۚ</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>64</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>يبعثوا</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2187,7 +4281,31 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>قُلۡ</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>64</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>قل</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2207,7 +4325,31 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>بَلَىٰ</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>64</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>بلى</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2227,7 +4369,31 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>94</v>
+        <v>89</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وَرَبِّي</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>64</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>وربي</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2247,7 +4413,31 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>95</v>
+        <v>90</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>لَتُبۡعَثُنَّ</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>64</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>لتبعثن</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2267,7 +4457,31 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ثُمَّ</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>64</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ثم</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2287,7 +4501,31 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>97</v>
+        <v>92</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>لَتُنَبَّؤُنَّ</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>64</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>7</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>لتنبؤن</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2307,7 +4545,31 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>98</v>
+        <v>93</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>بِمَا</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>64</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>7</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>بما</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2327,7 +4589,31 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>عَمِلۡتُمۡۚ</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>64</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>7</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>عملتم</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2347,7 +4633,31 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وَذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>64</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>وذلك</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2367,7 +4677,31 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>101</v>
+        <v>96</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>عَلَى</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>64</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>7</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>على</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2387,7 +4721,31 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>102</v>
+        <v>97</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>64</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>7</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2407,7 +4765,31 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>يَسِيرٞ</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>64</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>يسير</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2427,7 +4809,31 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>فَـَٔامِنُواْ</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>64</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>فآمنوا</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2447,7 +4853,31 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>بِٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>64</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>8</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>بالله</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2467,7 +4897,31 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>107</v>
+        <v>101</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>وَرَسُولِهِۦ</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>64</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ورسوله</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2487,7 +4941,31 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>108</v>
+        <v>102</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>وَٱلنُّورِ</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>64</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>والنور</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2507,7 +4985,31 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ٱلَّذِيٓ</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>64</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>8</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>الذي</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2527,7 +5029,31 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>أَنزَلۡنَاۚ</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>64</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>8</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>أنزلنا</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2547,7 +5073,31 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>111</v>
+        <v>105</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>وَٱللَّهُ</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>64</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>8</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>والله</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2567,7 +5117,31 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>بِمَا</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>64</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>8</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>بما</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2587,7 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>تَعۡمَلُونَ</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>64</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>8</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>تعملون</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2607,7 +5205,31 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>خَبِيرٞ</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>64</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>8</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>خبير</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2627,7 +5249,31 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>يَوۡمَ</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>64</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>9</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>يوم</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2647,7 +5293,31 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>118</v>
+        <v>111</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>يَجۡمَعُكُمۡ</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>64</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>9</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>يجمعكم</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2667,7 +5337,31 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>لِيَوۡمِ</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>64</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>9</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>ليوم</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2687,7 +5381,31 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ٱلۡجَمۡعِۖ</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>64</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>9</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>الجمع</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2707,7 +5425,31 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>64</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>9</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ذلك</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2727,7 +5469,31 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>يَوۡمُ</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>64</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>9</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>يوم</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2747,7 +5513,31 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>123</v>
+        <v>116</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ٱلتَّغَابُنِۗ</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>64</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>9</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>التغابن</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2767,7 +5557,31 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>64</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>9</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2787,7 +5601,31 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>125</v>
+        <v>118</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>يُؤۡمِنۢ</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>64</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>9</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>يؤمن</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2807,7 +5645,31 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>126</v>
+        <v>119</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>بِٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>64</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>9</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>بالله</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2827,7 +5689,31 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>وَيَعۡمَلۡ</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>64</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>9</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ويعمل</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2847,7 +5733,31 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>128</v>
+        <v>121</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>صَٰلِحٗا</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>64</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>9</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>صالحا</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2867,7 +5777,31 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>129</v>
+        <v>122</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>يُكَفِّرۡ</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>64</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>9</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>يكفر</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2887,7 +5821,31 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>عَنۡهُ</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>64</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>9</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>عنه</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2907,7 +5865,31 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>131</v>
+        <v>124</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>سَيِّـَٔاتِهِۦ</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>64</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>9</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>سيئاته</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2927,7 +5909,31 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>وَيُدۡخِلۡهُ</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>64</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>9</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ويدخله</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2947,7 +5953,31 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>133</v>
+        <v>126</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>جَنَّٰتٖ</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>64</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>9</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>جنات</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2967,12 +5997,36 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>134</v>
+        <v>127</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>تَجۡرِي</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>64</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>9</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>تجري</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>383.8030303030304</v>
+        <v>427.9568034557236</v>
       </c>
       <c r="B128" t="n">
         <v>743.2727272727274</v>
@@ -2987,18 +6041,42 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>135</v>
+        <v>128</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>مِن</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>64</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>9</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>326.2878787878788</v>
+        <v>383.8030303030304</v>
       </c>
       <c r="B129" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C129" t="n">
-        <v>383.8030303030304</v>
+        <v>427.9568034557236</v>
       </c>
       <c r="D129" t="n">
         <v>801.8939393939395</v>
@@ -3007,18 +6085,42 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>136</v>
+        <v>129</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>تَحۡتِهَا</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>64</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>9</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>تحتها</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>259.9242424242424</v>
+        <v>326.2878787878788</v>
       </c>
       <c r="B130" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C130" t="n">
-        <v>326.2878787878788</v>
+        <v>383.8030303030304</v>
       </c>
       <c r="D130" t="n">
         <v>801.8939393939395</v>
@@ -3027,18 +6129,42 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>137</v>
+        <v>130</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ٱلۡأَنۡهَٰرُ</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>64</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>9</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>الأنهار</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>225.6363636363637</v>
+        <v>259.9242424242424</v>
       </c>
       <c r="B131" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C131" t="n">
-        <v>259.9242424242424</v>
+        <v>326.2878787878788</v>
       </c>
       <c r="D131" t="n">
         <v>801.8939393939395</v>
@@ -3047,18 +6173,42 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>138</v>
+        <v>131</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>خَٰلِدِينَ</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>64</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>9</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>خالدين</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>191.3484848484849</v>
+        <v>225.6363636363637</v>
       </c>
       <c r="B132" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C132" t="n">
-        <v>225.6363636363637</v>
+        <v>259.9242424242424</v>
       </c>
       <c r="D132" t="n">
         <v>801.8939393939395</v>
@@ -3067,18 +6217,42 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>139</v>
+        <v>132</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>فِيهَآ</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>64</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>9</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>فيها</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>148.2121212121212</v>
+        <v>191.3484848484849</v>
       </c>
       <c r="B133" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C133" t="n">
-        <v>191.3484848484849</v>
+        <v>225.6363636363637</v>
       </c>
       <c r="D133" t="n">
         <v>801.8939393939395</v>
@@ -3087,18 +6261,42 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>140</v>
+        <v>133</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>أَبَدٗاۚ</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>64</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>9</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>أبدا</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>103.969696969697</v>
+        <v>148.2121212121212</v>
       </c>
       <c r="B134" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C134" t="n">
-        <v>148.2121212121212</v>
+        <v>191.3484848484849</v>
       </c>
       <c r="D134" t="n">
         <v>801.8939393939395</v>
@@ -3107,18 +6305,42 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>141</v>
+        <v>134</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>64</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>9</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>ذلك</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>45.34848484848485</v>
+        <v>103.969696969697</v>
       </c>
       <c r="B135" t="n">
         <v>743.2727272727274</v>
       </c>
       <c r="C135" t="n">
-        <v>103.969696969697</v>
+        <v>148.2121212121212</v>
       </c>
       <c r="D135" t="n">
         <v>801.8939393939395</v>
@@ -3127,7 +6349,75 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>142</v>
+        <v>135</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ٱلۡفَوۡزُ</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>64</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>9</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>الفوز</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>45.34848484848485</v>
+      </c>
+      <c r="B136" t="n">
+        <v>743.2727272727274</v>
+      </c>
+      <c r="C136" t="n">
+        <v>103.969696969697</v>
+      </c>
+      <c r="D136" t="n">
+        <v>801.8939393939395</v>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>136</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ٱلۡعَظِيمُ</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>64</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>التغَابُن</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>9</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>العظيم</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3232,7 +6522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4651,90 +7941,90 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>432.469696969697</v>
+        <v>427.9568034557236</v>
       </c>
       <c r="B129" t="n">
-        <v>213.469696969697</v>
+        <v>743.2727272727274</v>
       </c>
       <c r="C129" t="n">
-        <v>266.5606060606061</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>438.0000000000001</v>
+        <v>432.469696969697</v>
       </c>
       <c r="B130" t="n">
-        <v>640.409090909091</v>
+        <v>213.469696969697</v>
       </c>
       <c r="C130" t="n">
-        <v>696.8181818181819</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>444.6363636363637</v>
+        <v>438.0000000000001</v>
       </c>
       <c r="B131" t="n">
-        <v>266.5606060606061</v>
+        <v>640.409090909091</v>
       </c>
       <c r="C131" t="n">
-        <v>318.5454545454546</v>
+        <v>696.8181818181819</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>445.7424242424243</v>
+        <v>444.6363636363637</v>
       </c>
       <c r="B132" t="n">
-        <v>159.2727272727273</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C132" t="n">
-        <v>213.469696969697</v>
+        <v>318.5454545454546</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>449.0606060606061</v>
+        <v>445.7424242424243</v>
       </c>
       <c r="B133" t="n">
-        <v>107.2878787878788</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C133" t="n">
-        <v>159.2727272727273</v>
+        <v>213.469696969697</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>450.1666666666667</v>
+        <v>449.0606060606061</v>
       </c>
       <c r="B134" t="n">
-        <v>532.0151515151516</v>
+        <v>107.2878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>587.3181818181819</v>
+        <v>159.2727272727273</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>452.3787878787879</v>
+        <v>450.1666666666667</v>
       </c>
       <c r="B135" t="n">
-        <v>478.9242424242425</v>
+        <v>532.0151515151516</v>
       </c>
       <c r="C135" t="n">
-        <v>532.0151515151516</v>
+        <v>587.3181818181819</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>454.5909090909091</v>
+        <v>452.3787878787879</v>
       </c>
       <c r="B136" t="n">
-        <v>587.3181818181819</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C136" t="n">
-        <v>640.409090909091</v>
+        <v>532.0151515151516</v>
       </c>
     </row>
     <row r="137">
@@ -4742,87 +8032,87 @@
         <v>454.5909090909091</v>
       </c>
       <c r="B137" t="n">
-        <v>743.2727272727274</v>
+        <v>587.3181818181819</v>
       </c>
       <c r="C137" t="n">
-        <v>801.8939393939395</v>
+        <v>640.409090909091</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>459.0151515151516</v>
+        <v>454.5909090909091</v>
       </c>
       <c r="B138" t="n">
-        <v>429.1515151515152</v>
+        <v>743.2727272727274</v>
       </c>
       <c r="C138" t="n">
-        <v>478.9242424242425</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>460.1212121212122</v>
+        <v>459.0151515151516</v>
       </c>
       <c r="B139" t="n">
-        <v>213.469696969697</v>
+        <v>429.1515151515152</v>
       </c>
       <c r="C139" t="n">
-        <v>266.5606060606061</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>464.5454545454546</v>
+        <v>460.1212121212122</v>
       </c>
       <c r="B140" t="n">
-        <v>370.5303030303031</v>
+        <v>213.469696969697</v>
       </c>
       <c r="C140" t="n">
-        <v>429.1515151515152</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>465.6515151515152</v>
+        <v>464.5454545454546</v>
       </c>
       <c r="B141" t="n">
-        <v>696.8181818181819</v>
+        <v>370.5303030303031</v>
       </c>
       <c r="C141" t="n">
-        <v>743.2727272727274</v>
+        <v>429.1515151515152</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>470.0757575757576</v>
+        <v>465.6515151515152</v>
       </c>
       <c r="B142" t="n">
-        <v>159.2727272727273</v>
+        <v>696.8181818181819</v>
       </c>
       <c r="C142" t="n">
-        <v>213.469696969697</v>
+        <v>743.2727272727274</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>481.1363636363637</v>
+        <v>470.0757575757576</v>
       </c>
       <c r="B143" t="n">
-        <v>318.5454545454546</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C143" t="n">
-        <v>370.5303030303031</v>
+        <v>213.469696969697</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>499.939393939394</v>
+        <v>481.1363636363637</v>
       </c>
       <c r="B144" t="n">
-        <v>213.469696969697</v>
+        <v>318.5454545454546</v>
       </c>
       <c r="C144" t="n">
-        <v>266.5606060606061</v>
+        <v>370.5303030303031</v>
       </c>
     </row>
     <row r="145">
@@ -4830,10 +8120,10 @@
         <v>499.939393939394</v>
       </c>
       <c r="B145" t="n">
-        <v>370.5303030303031</v>
+        <v>213.469696969697</v>
       </c>
       <c r="C145" t="n">
-        <v>429.1515151515152</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="146">
@@ -4841,10 +8131,10 @@
         <v>499.939393939394</v>
       </c>
       <c r="B146" t="n">
+        <v>370.5303030303031</v>
+      </c>
+      <c r="C146" t="n">
         <v>429.1515151515152</v>
-      </c>
-      <c r="C146" t="n">
-        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="147">
@@ -4852,21 +8142,21 @@
         <v>499.939393939394</v>
       </c>
       <c r="B147" t="n">
+        <v>429.1515151515152</v>
+      </c>
+      <c r="C147" t="n">
         <v>478.9242424242425</v>
-      </c>
-      <c r="C147" t="n">
-        <v>532.0151515151516</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>501.0454545454546</v>
+        <v>499.939393939394</v>
       </c>
       <c r="B148" t="n">
-        <v>107.2878787878788</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C148" t="n">
-        <v>159.2727272727273</v>
+        <v>532.0151515151516</v>
       </c>
     </row>
     <row r="149">
@@ -4874,10 +8164,10 @@
         <v>501.0454545454546</v>
       </c>
       <c r="B149" t="n">
+        <v>107.2878787878788</v>
+      </c>
+      <c r="C149" t="n">
         <v>159.2727272727273</v>
-      </c>
-      <c r="C149" t="n">
-        <v>213.469696969697</v>
       </c>
     </row>
     <row r="150">
@@ -4885,10 +8175,10 @@
         <v>501.0454545454546</v>
       </c>
       <c r="B150" t="n">
-        <v>266.5606060606061</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C150" t="n">
-        <v>318.5454545454546</v>
+        <v>213.469696969697</v>
       </c>
     </row>
     <row r="151">
@@ -4896,21 +8186,21 @@
         <v>501.0454545454546</v>
       </c>
       <c r="B151" t="n">
-        <v>696.8181818181819</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C151" t="n">
-        <v>743.2727272727274</v>
+        <v>318.5454545454546</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>502.1515151515152</v>
+        <v>501.0454545454546</v>
       </c>
       <c r="B152" t="n">
-        <v>587.3181818181819</v>
+        <v>696.8181818181819</v>
       </c>
       <c r="C152" t="n">
-        <v>640.409090909091</v>
+        <v>743.2727272727274</v>
       </c>
     </row>
     <row r="153">
@@ -4918,10 +8208,10 @@
         <v>502.1515151515152</v>
       </c>
       <c r="B153" t="n">
+        <v>587.3181818181819</v>
+      </c>
+      <c r="C153" t="n">
         <v>640.409090909091</v>
-      </c>
-      <c r="C153" t="n">
-        <v>696.8181818181819</v>
       </c>
     </row>
     <row r="154">
@@ -4929,31 +8219,42 @@
         <v>502.1515151515152</v>
       </c>
       <c r="B154" t="n">
-        <v>743.2727272727274</v>
+        <v>640.409090909091</v>
       </c>
       <c r="C154" t="n">
-        <v>801.8939393939395</v>
+        <v>696.8181818181819</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>503.2575757575758</v>
+        <v>502.1515151515152</v>
       </c>
       <c r="B155" t="n">
-        <v>532.0151515151516</v>
+        <v>743.2727272727274</v>
       </c>
       <c r="C155" t="n">
-        <v>587.3181818181819</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
+        <v>503.2575757575758</v>
+      </c>
+      <c r="B156" t="n">
+        <v>532.0151515151516</v>
+      </c>
+      <c r="C156" t="n">
+        <v>587.3181818181819</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
         <v>504.3636363636364</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B157" t="n">
         <v>318.5454545454546</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C157" t="n">
         <v>370.5303030303031</v>
       </c>
     </row>
